--- a/HUS_APP/Casos_de_Prueba.xlsx
+++ b/HUS_APP/Casos_de_Prueba.xlsx
@@ -65,7 +65,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -87,11 +87,55 @@
         <color rgb="00B4B4B4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,6 +158,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -502,16 +548,25 @@
           <t>Trazabilidad</t>
         </is>
       </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="9" t="n"/>
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Diseño de la prueba</t>
         </is>
       </c>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="9" t="n"/>
       <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Ejecución</t>
         </is>
       </c>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="9" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1505,20 +1560,19 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Edición exitosa</t>
+          <t>Edicion exitosa y verificable</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>El usuario abre el modal de edición de un estudiante</t>
+          <t>El usuario abre la edicion de un estudiante ya registrado</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>1. Iniciar sesión con el rol Docente o Administrador.
-2. El usuario abre el modal de edición de un estudiante.
-3. Modifica uno o más campos y confirma en el diálogo.
-4. Observar la respuesta del sistema.</t>
+          <t>1. Iniciar sesion con el rol Docente o Administrador.
+2. El usuario abre la edicion de un estudiante ya registrado.
+3. Modifica uno o varios de los campos editables (nombre, apellido, edad, nivel, grado, ano de cursada, genero, contacto de emergencia, tipo y numero de documento) y confirma en el dialogo.</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1528,7 +1582,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>El sistema guarda los cambios y muestra «Alumno actualizado correctamente»</t>
+          <t>El sistema guarda los cambios, muestra «Alumno actualizado correctamente» y el listado refleja de inmediato los valores nuevos, de modo que el resultado se puede verificar sin recargar la pagina</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1676,20 +1730,19 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Eliminación de un registro sin historial</t>
+          <t>Eliminacion de un registro sin historial</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>El estudiante no tiene notas, encuestas, predicciones ni expediente</t>
+          <t>El estudiante seleccionado no tiene notas, encuestas, predicciones ni expediente</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>1. Iniciar sesión con el rol Docente o Administrador.
-2. El estudiante no tiene notas, encuestas, predicciones ni expediente.
-3. El usuario pulsa «Eliminar» y confirma.
-4. Observar la respuesta del sistema.</t>
+          <t>1. Iniciar sesion con el rol Docente o Administrador.
+2. El estudiante seleccionado no tiene notas, encuestas, predicciones ni expediente.
+3. El usuario pulsa «Eliminar» y confirma en el dialogo.</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -1699,7 +1752,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>El sistema elimina el registro y actualiza el listado</t>
+          <t>El sistema responde 204, retira al estudiante del listado y el total de registrados disminuye en uno</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1733,7 +1786,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Eliminación bloqueada por historial</t>
+          <t>Eliminacion bloqueada, sin borrado en cascada</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1743,10 +1796,9 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>1. Iniciar sesión con el rol Docente o Administrador.
+          <t>1. Iniciar sesion con el rol Docente o Administrador.
 2. El estudiante tiene notas, encuestas o predicciones registradas.
-3. El usuario pulsa «Eliminar» y confirma.
-4. Observar la respuesta del sistema.</t>
+3. El usuario pulsa «Eliminar» y confirma.</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1756,7 +1808,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>El sistema responde 409 detallando cuántos registros de cada tipo lo impiden</t>
+          <t>El sistema responde 409 SIN borrar nada: ni el estudiante ni sus notas, encuestas, predicciones, inasistencias o expediente. El mensaje enumera cuantos registros de cada tipo lo impiden. Para darlo de baja hay que retirar antes ese historial de forma deliberada</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1769,8 +1821,16 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. 409 y NO borra en cascada: 1 encuesta antes, 1 despues</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1904,20 +1964,19 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Ítem fuera de escala</t>
+          <t>Item fuera de la escala EDAH</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Se envía un ítem con valor 4</t>
+          <t>Se envia un item con un valor distinto de 0, 1, 2 o 3</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>1. Iniciar sesión con el rol Psicólogo.
-2. Se envía un ítem con valor 4.
-3. Se intenta guardar la encuesta.
-4. Observar la respuesta del sistema.</t>
+          <t>1. Iniciar sesion con el rol Psicólogo.
+2. Se envia un item con un valor distinto de 0, 1, 2 o 3.
+3. Se intenta guardar la encuesta.</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1927,7 +1986,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>El sistema rechaza el envío: los ítems solo admiten valores de 0 a 3</t>
+          <t>El sistema rechaza el envio con 422 indicando que los items solo admiten valores de 0 a 3. Los totales por subescala (DA, HI, TC) los calcula el sistema al guardar; no son campos que el usuario introduzca ni pueda corregir</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1940,8 +1999,16 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. valor 4 -&gt; HTTP 422; los totales los calcula el sistema (DA=5 HI=5 TC=0)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1961,20 +2028,19 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Ítem sin responder</t>
+          <t>No se admite una encuesta incompleta</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Falta uno de los 20 ítems</t>
+          <t>Falta por responder al menos uno de los 20 items</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>1. Iniciar sesión con el rol Psicólogo.
-2. Falta uno de los 20 ítems.
-3. Se intenta guardar la encuesta.
-4. Observar la respuesta del sistema.</t>
+          <t>1. Iniciar sesion con el rol Psicólogo.
+2. Falta por responder al menos uno de los 20 items.
+3. Se intenta guardar la encuesta.</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1984,7 +2050,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>El sistema indica que el campo es obligatorio y no guarda</t>
+          <t>El sistema rechaza el guardado con 422 y no almacena nada parcial: el EDAH solo es interpretable completo, y una encuesta a medias produciria una puntuacion falsamente baja. No existe la figura de borrador</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -1997,8 +2063,16 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. falta un item -&gt; HTTP 422, no se guarda nada parcial</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2075,20 +2149,19 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Registro exitoso</t>
+          <t>Registro de los dias del ano lectivo</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>El docente selecciona un estudiante y escribe los días</t>
+          <t>El docente selecciona un estudiante y consulta su valor vigente</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>1. Iniciar sesión con el rol Docente.
-2. El docente selecciona un estudiante y escribe los días.
-3. Confirma en el diálogo.
-4. Observar la respuesta del sistema.</t>
+          <t>1. Iniciar sesion con el rol Docente.
+2. El docente selecciona un estudiante y consulta su valor vigente.
+3. Escribe los dias de inasistencia acumulados en el ano lectivo y confirma.</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -2098,7 +2171,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>El sistema guarda el valor y recalcula la predicción del estudiante</t>
+          <t>El sistema guarda el valor, deja constancia del cambio en el historial y recalcula la prediccion. La interfaz indica que el periodo es el ano lectivo completo, no el bimestre, y que el maximo admitido es 365 dias</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2111,8 +2184,16 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. periodo declarado: ano lectivo 2025, maximo 365</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3937,6 +4018,1736 @@
       </c>
       <c r="K61" s="5" t="inlineStr"/>
       <c r="L61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>CP0060</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>HU0020-1</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Solicitud registrada</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>El usuario olvido su contrasena y esta en la pantalla de acceso</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la pantalla de acceso sin iniciar sesion.
+2. Pulsar «¿Olvidaste tu contrasena?».
+3. Escribir el usuario propio y enviar la solicitud.</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Usuario del sistema. Escenario 1 de HU0020.</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>El sistema registra la peticion, la deja pendiente durante 72 horas e indica que debe acudir al administrador; no se envia ningun correo ni mensaje</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. HTTP 200; la peticion queda registrada</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CP0061</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>HU0020-2</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>La respuesta no revela si la cuenta existe</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Alguien escribe un usuario que no esta registrado</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la pantalla de acceso sin iniciar sesion.
+2. Pulsar «¿Olvidaste tu contrasena?».
+3. Escribir un usuario inexistente y enviar la solicitud.
+4. Repetir con un usuario que si existe y comparar los dos mensajes.</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Usuario del sistema. Escenario 2 de HU0020.</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>El sistema responde exactamente el mismo mensaje que para una cuenta real, de modo que no se pueda averiguar que usuarios existen probando nombres</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. el mensaje es identico para una cuenta real y para una inexistente</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>CP0062</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>HU0020-3</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Una sola peticion viva por cuenta</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>El usuario ya tiene una solicitud pendiente sin atender</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>1. Solicitar el restablecimiento de una cuenta.
+2. Volver a solicitarlo para la misma cuenta antes de que la atiendan.
+3. Iniciar sesion como Administrador y abrir «Accesos y Seguridad».</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Usuario del sistema. Escenario 3 de HU0020.</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>El sistema renueva la vigencia de la peticion existente en lugar de crear otra, para que la bandeja del administrador no acumule duplicados</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. tras dos solicitudes seguidas queda 1 pendiente, no dos</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>CP0063</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>HU0020</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>HU0020-4</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>La solicitud caduca sola</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Han pasado mas de 72 horas desde la peticion</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>1. Disponer de una solicitud con mas de 72 horas de antiguedad.
+2. Iniciar sesion como Administrador.
+3. Abrir «Accesos y Seguridad» y revisar la bandeja de solicitudes.</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Usuario del sistema. Escenario 4 de HU0020.</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>La peticion aparece como «caducada» y ya no se puede atender, sin que nadie haya tenido que ejecutar ninguna tarea de limpieza</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente de comprobacion visual: caducidad a 72 h: requiere esperar o manipular la fecha</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>CP0064</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>HU0021-1</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Solo el administrador accede a la bandeja</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Un docente o un psicologo inicia sesion</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente (o Psicologo).
+2. Comprobar que «Accesos y Seguridad» no aparece en el menu.
+3. Llamar directamente a la API de accesos con ese token.</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 1 de HU0021.</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>El sistema deniega el acceso con codigo 403; la comprobacion se hace en el servidor y no depende de que la opcion este oculta en el menu</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. un docente recibe 403 y 403 en las dos rutas de administracion</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>CP0065</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>HU0021-2</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Restablecimiento aplicado</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Existe una solicitud pendiente de un usuario</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. Existe una solicitud pendiente de un usuario.
+3. El administrador escribe la contrasena nueva y confirma en el dialogo.</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 2 de HU0021.</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>El sistema guarda la contrasena cifrada, marca la solicitud como atendida e indica que debe comunicarse en persona porque no se envia por ningun medio</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. restablecida (HTTP 200) y la cuenta entra con la nueva (HTTP 200)</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>CP0066</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>HU0021-3</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Las sesiones abiertas se cierran</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>El usuario afectado tenia sesiones activas en otros equipos</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con la cuenta afectada en otro navegador.
+2. Iniciar sesion como Administrador y atender su solicitud.
+3. Volver al primer navegador e intentar cualquier accion.</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 3 de HU0021.</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>El sistema revoca todas sus sesiones, porque si pidio recuperar el acceso cabe la posibilidad de que otra persona lo tuviera</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. el token anterior al restablecimiento ya no sirve (HTTP 401)</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>CP0067</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>HU0021-4</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Una solicitud atendida no se reutiliza</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>La solicitud ya fue atendida o caduco</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. La solicitud ya fue atendida o caduco.
+3. Se intenta atenderla de nuevo.</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 4 de HU0021.</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>El sistema responde con codigo 409 e indica en que estado se encuentra, en lugar de cambiar la contrasena por segunda vez</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. atender dos veces la misma solicitud devuelve HTTP 409</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>CP0068</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>HU0021</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>HU0021-5</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>La contrasena nueva debe ser valida</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>El administrador esta atendiendo una solicitud</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. El administrador esta atendiendo una solicitud.
+3. Escribe una contrasena que no cumple la longitud minima.</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 5 de HU0021.</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>El sistema la rechaza explicando el motivo y la solicitud sigue pendiente</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. una contrasena demasiado corta se rechaza (HTTP 400)</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>CP0069</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>HU0022-1</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Inventario de cuentas</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>El administrador entra en «Accesos y Seguridad»</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. El administrador entra en «Accesos y Seguridad».
+3. Consulta la seccion de cuentas del sistema.</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 1 de HU0022.</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>El sistema lista cada cuenta con su rol, su ultimo acceso y cuantas sesiones tiene abiertas en ese momento</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. 3 cuentas con rol, ultimo acceso y sesiones abiertas</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CP0070</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>HU0022-2</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Cierre de sesiones sin cambiar la contrasena</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Una cuenta tiene sesiones abiertas</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. Una cuenta tiene sesiones abiertas.
+3. El administrador pulsa «Cerrar sesiones» y confirma.</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 2 de HU0022.</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>El sistema revoca esas sesiones y la contrasena permanece intacta, de modo que la persona puede volver a entrar con la que ya conoce</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. sesiones 2 -&gt; 0; la contrasena sigue sirviendo (HTTP 200)</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>CP0071</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>HU0022-3</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Aviso al cerrar la propia sesion</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>El administrador va a cerrar las sesiones de su propia cuenta</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. Abrir «Accesos y Seguridad».
+3. Pulsar «Cerrar sesiones» en la fila de la propia cuenta.</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 3 de HU0022.</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>El sistema advierte de que se cerrara tambien la suya y tendra que volver a entrar</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente de comprobacion visual: aviso al cerrar la propia sesion: es texto del dialogo</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>CP0072</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>HU0022</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>HU0022-4</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Matriz de permisos derivada de la configuracion</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>El administrador consulta que ve cada rol</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Administrador.
+2. El administrador consulta que ve cada rol.
+3. Revisa la tabla de permisos.</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Administrador. Escenario 4 de HU0022.</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>La tabla se genera a partir de la configuracion real de permisos y no de un texto escrito a mano, de modo que no puede quedar desfasada respecto al sistema</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente de comprobacion visual: matriz de permisos: se genera en el navegador desde rbac.js</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>CP0073</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>HU0023-1</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Fiabilidad medida con estudiantes reales</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>El usuario abre «Metricas del Modelo»</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Psicologo.
+2. El usuario abre «Metricas del Modelo».
+3. Consulta el encabezado de cada modelo.</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Psicologo. Escenario 1 de HU0023.</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>El sistema muestra el porcentaje de acierto sobre los 30 estudiantes reales, con su matriz de confusion y el desglose por nivel</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. TDAH 0.9333 y riesgo 0.8667 sobre 30 reales</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>CP0074</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>HU0023-2</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Se distinguen los dos conjuntos de datos</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Conviven la validacion de entrenamiento y la validacion real</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Psicologo.
+2. Conviven la validacion de entrenamiento y la validacion real.
+3. El usuario recorre la pantalla.</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Psicologo. Escenario 2 de HU0023.</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>El sistema separa y explica ambas: 500 registros sinteticos repartidos en 400 de entrenamiento y 100 de validacion, frente a 30 estudiantes reales con dictamen profesional, indicando para que sirve cada una</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. conviven los 30 reales y los 400+100 sinteticos</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>CP0075</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>HU0023-3</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Influencia de cada variable</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>El usuario quiere saber en que se fija el modelo</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Psicologo.
+2. El usuario quiere saber en que se fija el modelo.
+3. Consulta la seccion de influencia.</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Psicologo. Escenario 3 de HU0023.</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>El sistema muestra el peso de cada variable del modelo de riesgo y de cada subescala del EDAH, aclarando que explica el modelo en conjunto y no un caso concreto</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. 3 variables de riesgo y 3 subescalas EDAH con su peso</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>CP0076</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>HU0023-4</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Advertencia de tamizaje</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>El usuario consulta cualquier cifra de la pantalla</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Psicologo.
+2. El usuario consulta cualquier cifra de la pantalla.
+3. Lee el encabezado y el cierre de la vista.</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Psicologo. Escenario 4 de HU0023.</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>El sistema advierte de que es una herramienta de tamizaje y no de diagnostico, y explica que consecuencia tiene cada tipo de error</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. el aviso de tamizaje viaja con los datos, no solo en la interfaz</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>CP0077</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>HU0023</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>HU0023-5</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Aviso en los niveles con pocos casos</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Un nivel de la validacion real tiene menos de cinco estudiantes</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Psicologo.
+2. Un nivel de la validacion real tiene menos de cinco estudiantes.
+3. El usuario consulta el desglose por nivel.</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Psicologo. Escenario 5 de HU0023.</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>El sistema advierte de que ese porcentaje es poco fiable, porque un solo acierto o fallo lo mueve decenas de puntos</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. hay niveles con pocos casos que la interfaz debe advertir: Probabilidad Media</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>CP0078</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>HU0006</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>HU0006-4</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Validacion al editar</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>El usuario esta editando un estudiante</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Administrador.
+2. Abrir la edicion de un estudiante registrado.
+3. Escribir una edad fuera del rango 11-12 y guardar.
+4. Repetir con un grado que no corresponde al nivel.</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Administrador. Escenario 4 de HU0006.</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>El sistema rechaza el guardado —422 cuando el valor incumple el formato del campo, como una edad fuera de 11-12; 400 cuando la combinacion no es valida, como un grado que no corresponde al nivel— explicando el motivo, y los datos anteriores del estudiante permanecen sin cambios</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. edad fuera de rango -&gt; 422; grado que no corresponde al nivel -&gt; 400; el alumno conserva sus valores</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CP0079</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>HU0006</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>HU0006-5</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Cancelacion de la edicion</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>El usuario ha modificado campos pero aun no ha confirmado</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Administrador.
+2. El usuario ha modificado campos pero aun no ha confirmado.
+3. Pulsa «Cancelar» o cierra el dialogo con Escape.</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Administrador. Escenario 5 de HU0006.</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>No se envia ninguna peticion y el estudiante conserva sus valores originales</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente de comprobacion visual: Cancelacion de la edicion: es comportamiento del dialogo, se comprueba en pantalla</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>CP0080</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>HU0007</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>HU0007-4</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Cancelacion de la eliminacion</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>El dialogo de confirmacion de borrado esta abierto</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente o Administrador.
+2. El dialogo de confirmacion de borrado esta abierto.
+3. El usuario pulsa «Cancelar» o la tecla Escape.</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente o Administrador. Escenario 4 de HU0007.</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>No se envia ninguna peticion, el estudiante sigue registrado y el listado no cambia. El foco inicial del dialogo esta en «Cancelar» para que un Enter accidental no ejecute el borrado</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente de comprobacion visual: Cancelacion del borrado y foco en «Cancelar»: se comprueba en pantalla</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>CP0081</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>HU0008-5</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Se registra quien responde la escala</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>El EDAH lo responde un adulto que observa al estudiante a diario, no el propio estudiante</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Psicólogo.
+2. El EDAH lo responde un adulto que observa al estudiante a diario, no el propio estudiante.
+3. Se guarda la encuesta indicando el informante: docente, familiar o psicologo por observacion directa.</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Psicólogo. Escenario 5 de HU0008.</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>El sistema almacena el informante junto a la encuesta y lo muestra al consultarla. Una misma puntuacion no se interpreta igual segun quien la responda, porque la conducta en clase y en casa no son lo mismo</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. la encuesta guarda el informante: 'Docente'</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>CP0082</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>HU0008-6</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Informante no admitido</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Se envia un informante que no esta en la lista prevista</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Psicólogo.
+2. Se envia un informante que no esta en la lista prevista.
+3. Se intenta guardar la encuesta.</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Psicólogo. Escenario 6 de HU0008.</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>El sistema rechaza el envio con 422 y enumera los informantes admitidos</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. informante fuera de la lista -&gt; HTTP 422</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>CP0083</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>HU0008</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>HU0008-7</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Reaplicacion: se usa siempre la mas reciente</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante ya tiene una encuesta registrada</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Psicólogo.
+2. El estudiante ya tiene una encuesta registrada.
+3. Se registra una encuesta nueva para el mismo estudiante.</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Psicólogo. Escenario 7 de HU0008.</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>El sistema NO sobrescribe la anterior: la conserva y anade la nueva, porque el EDAH se reaplica en el tiempo y comparar dos momentos es parte de la evaluacion. Las predicciones usan siempre la mas reciente por fecha, y a igualdad de fecha la ultima registrada. Una encuesta guardada no se puede corregir: si hubo un error, se aplica de nuevo</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. 2 encuestas conservadas; la primera de la lista es la mas reciente (id=45)</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>CP0084</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>HU0009</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>HU0009-5</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Consulta del historial de cambios</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>El docente selecciona un estudiante en Control de Inasistencias</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente.
+2. El docente selecciona un estudiante en Control de Inasistencias.
+3. Consulta el panel de historial.</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente. Escenario 5 de HU0009.</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>El sistema muestra cada cambio del contador con su valor anterior, el nuevo, la diferencia, la fecha y quien lo registro. Sin esto solo se conservaria el ultimo numero y no habria forma de distinguir una correccion de captura de un empeoramiento real del estudiante</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. 2 movimientos con antes/despues/quien/cuando</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>CP0085</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>HU0009</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>HU0009-6</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Aviso ante un salto grande</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Se registra un cambio de 15 dias o mas en una sola anotacion</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Docente.
+2. Se registra un cambio de 15 dias o mas en una sola anotacion.
+3. El docente consulta el historial.</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Docente. Escenario 6 de HU0009.</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>El sistema destaca ese movimiento, porque un salto asi se parece tanto a un mes de ausencias real como a un cero de mas al teclear, y la cifra alimenta el modelo de riesgo</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. el salto de 25 dias queda identificable en el historial</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>CP0086</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>HU0012</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>HU0012-4</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Cualquier rol con acceso puede generarla</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Tanto el docente como el psicologo y el administrador tienen la vista de predicciones</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesion con el rol Usuario del sistema.
+2. Tanto el docente como el psicologo y el administrador tienen la vista de predicciones.
+3. Cualquiera de ellos solicita generar la prediccion de un estudiante.</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Rol: Usuario del sistema. Escenario 4 de HU0012.</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>El sistema la genera sin distinguir el rol: no es un acto clinico reservado, sino el calculo de un modelo. Ademas se regenera sola cuando cambian las notas o las inasistencias, de modo que tambien la desencadena el docente sin pedirla expresamente</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Verificado contra el sistema desplegado. docente -&gt; HTTP 200, administrador -&gt; HTTP 200</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
